--- a/AAII_Financials/Quarterly/ASOZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASOZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
   <si>
     <t>ASOZY</t>
   </si>
@@ -656,77 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -766,8 +777,17 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +827,17 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +877,17 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +903,11 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +947,17 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +997,17 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1047,17 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1097,17 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1120,11 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,8 +1164,17 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1125,8 +1214,17 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1240,11 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1183,8 +1284,17 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,8 +1334,17 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1384,17 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1306,8 +1434,17 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1484,17 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1534,17 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1429,8 +1584,17 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1634,17 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1684,17 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1734,17 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1784,17 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1834,17 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1675,8 +1884,17 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1716,8 +1934,17 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1984,17 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,54 +2034,72 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2115,11 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,377 +2135,461 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1356700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1766300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2016400</v>
+      </c>
+      <c r="G41" s="3">
         <v>744800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>683500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>793900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>798300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>700000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>655800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>737000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>759800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>594000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>626200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>740500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>830400</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F42" s="3">
+        <v>18700</v>
+      </c>
+      <c r="G42" s="3">
         <v>8200</v>
       </c>
-      <c r="E42" s="3">
-        <v>900</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>56700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
         <v>42700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>81300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>78300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>1200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>1200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="Q42" s="3">
         <v>1100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="R42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1274000</v>
+        <v>1430900</v>
       </c>
       <c r="E43" s="3">
-        <v>1409700</v>
+        <v>1536700</v>
       </c>
       <c r="F43" s="3">
+        <v>1236700</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1373000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1394500</v>
+      </c>
+      <c r="I43" s="3">
         <v>1346900</v>
       </c>
-      <c r="G43" s="3">
-        <v>1243300</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
+        <v>1239400</v>
+      </c>
+      <c r="K43" s="3">
         <v>1208500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>1232200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>1183700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>1181600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>1201400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>1275000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>1220300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>1121200</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>104300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>91500</v>
+      </c>
+      <c r="F44" s="3">
+        <v>90200</v>
+      </c>
+      <c r="G44" s="3">
         <v>84100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>101800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>104900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>90600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>68400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>70400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>68600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>82900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>80600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>78700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>80500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>74500</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>119400</v>
+      </c>
+      <c r="F45" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G45" s="3">
         <v>660700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>3300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
         <v>14800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3">
         <v>7800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>7700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>8600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>16700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>17500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>19000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>18400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="R45" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3078500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3515300</v>
+      </c>
+      <c r="F46" s="3">
+        <v>3467600</v>
+      </c>
+      <c r="G46" s="3">
         <v>2870800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>2313000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>2360000</v>
       </c>
-      <c r="G46" s="3">
-        <v>2290200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
+        <v>2290000</v>
+      </c>
+      <c r="K46" s="3">
         <v>2108800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>2054800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>2165500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>2192400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>1957900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>2064200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>2137600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>2140000</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>407700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>407900</v>
+      </c>
+      <c r="F47" s="3">
+        <v>390800</v>
+      </c>
+      <c r="G47" s="3">
         <v>74300</v>
       </c>
-      <c r="E47" s="3">
-        <v>70500</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
+        <v>72200</v>
+      </c>
+      <c r="I47" s="3">
         <v>72700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
         <v>79300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>75100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>56600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>64500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>58700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>55900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>58100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>49400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="R47" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>482900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>474900</v>
+      </c>
+      <c r="F48" s="3">
+        <v>479500</v>
+      </c>
+      <c r="G48" s="3">
         <v>490100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>521100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>469800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>454300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>482400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>425600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>428500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>437400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>394100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>421600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>413100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>407200</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1976300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1955700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1977600</v>
+      </c>
+      <c r="G49" s="3">
         <v>1969800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>2346800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>2101300</v>
       </c>
-      <c r="G49" s="3">
-        <v>1995000</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
+        <v>1996300</v>
+      </c>
+      <c r="K49" s="3">
         <v>2046200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>1945100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>1964200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>2002100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>1844300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>1958700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>1901700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>1900700</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2629,17 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2679,67 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>51200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>42500</v>
+      </c>
+      <c r="G52" s="3">
         <v>55900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>62200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>56600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>33100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>45200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>36600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>38600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>30200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>31600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>30700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>24500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2779,67 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6052600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6455100</v>
+      </c>
+      <c r="F54" s="3">
+        <v>6417900</v>
+      </c>
+      <c r="G54" s="3">
         <v>5508100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>5383900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>5124700</v>
       </c>
-      <c r="G54" s="3">
-        <v>4917700</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
+        <v>4918800</v>
+      </c>
+      <c r="K54" s="3">
         <v>4809400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>4585500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>4729300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>4780200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>4351600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>4612100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>4602600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>4597500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2855,11 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,254 +2875,311 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>512900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>523600</v>
+      </c>
+      <c r="F57" s="3">
+        <v>542500</v>
+      </c>
+      <c r="G57" s="3">
         <v>451800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>440300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>441800</v>
       </c>
-      <c r="G57" s="3">
-        <v>449200</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
+        <v>449300</v>
+      </c>
+      <c r="K57" s="3">
         <v>347500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>329100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>329900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>416400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>334500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>338800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>321100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>363800</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>415300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>438900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>380500</v>
+      </c>
+      <c r="G58" s="3">
         <v>383200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>415200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>369200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>348000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>355100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>338500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>348400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>339800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>346600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>335900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>335200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="R58" s="3">
         <v>321200</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>631400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>626400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>645500</v>
+      </c>
+      <c r="G59" s="3">
         <v>750000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>619100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>585100</v>
       </c>
-      <c r="G59" s="3">
-        <v>523500</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>525200</v>
+      </c>
+      <c r="K59" s="3">
         <v>461600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>490200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>539100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>448600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>390100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>429500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>486800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>445100</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1963100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1970500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1985300</v>
+      </c>
+      <c r="G60" s="3">
         <v>1925700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>1844200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>1749600</v>
       </c>
-      <c r="G60" s="3">
-        <v>1686900</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
+        <v>1688700</v>
+      </c>
+      <c r="K60" s="3">
         <v>1477100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>1452900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>1530300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>1534700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>1344900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>1389100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>1425000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>1437500</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>551600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>547200</v>
+      </c>
+      <c r="F61" s="3">
+        <v>540200</v>
+      </c>
+      <c r="G61" s="3">
         <v>604800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>634900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>588900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>598800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>689500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>629900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>635000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>702300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>687700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>537600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>542600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>584100</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>141700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>122100</v>
+      </c>
+      <c r="G62" s="3">
         <v>110300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>198300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>190100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>146400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>149500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>74300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>85000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>81900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>78400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>81400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>84100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3219,17 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3269,17 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3319,67 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2827100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2835700</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2830200</v>
+      </c>
+      <c r="G66" s="3">
         <v>2776800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>2835900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>2683400</v>
       </c>
-      <c r="G66" s="3">
-        <v>2583100</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
+        <v>2584900</v>
+      </c>
+      <c r="K66" s="3">
         <v>2456300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>2307200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>2407300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>2472100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>2248400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>2168400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>2211200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>2265000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3395,11 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3439,17 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3489,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3539,17 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3589,67 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>805500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1041900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>1015800</v>
+      </c>
+      <c r="G72" s="3">
         <v>799800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>758400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>738800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>660300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>670200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>607800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>649300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>624300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>531600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>543400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>549600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>515600</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3689,17 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3739,17 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3789,67 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1849400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2090000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2066400</v>
+      </c>
+      <c r="G76" s="3">
         <v>1550900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>1488200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>1427600</v>
       </c>
-      <c r="G76" s="3">
-        <v>1329900</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
+        <v>1329400</v>
+      </c>
+      <c r="K76" s="3">
         <v>1374000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>1312800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>1358900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>1348800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>1227200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>1557200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>1540100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>1495800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3889,72 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,8 +3994,17 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +4020,61 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>33900</v>
       </c>
       <c r="F83" s="3">
+        <v>22300</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>51700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>25200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>49600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>53500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>52300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>25900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>47300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>24400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>27000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="R83" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +4114,17 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +4164,17 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4214,17 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4264,17 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4314,67 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>4</v>
+      <c r="D89" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-50300</v>
       </c>
       <c r="F89" s="3">
+        <v>409100</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
+        <v>105900</v>
+      </c>
+      <c r="I89" s="3">
         <v>107700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>289300</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>86300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>317400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>127800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>92500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>71300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,49 +4390,61 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-12700</v>
       </c>
       <c r="F91" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
+        <v>-14700</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-11800</v>
       </c>
       <c r="J91" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-9800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-15200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-9300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-11900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-13600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="R91" s="3">
         <v>-17900</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4484,17 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4534,67 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-202000</v>
       </c>
       <c r="F94" s="3">
+        <v>630200</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-71300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-68900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-63000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-13800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-47600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-58700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-106900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,49 +4610,61 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>279200</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
+        <v>74400</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>71500</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4704,17 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4754,17 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,127 +4804,163 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>-590800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>28800</v>
       </c>
       <c r="F100" s="3">
+        <v>124300</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-204100</v>
+      </c>
+      <c r="I100" s="3">
         <v>-68800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>-107600</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>-81900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-116400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-133700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-161300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-53400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>-49200</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-34800</v>
       </c>
       <c r="F101" s="3">
+        <v>32500</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-47800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>17400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>-32100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-18900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-72500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>45000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>6200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>13800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="R101" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-391300</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-173500</v>
       </c>
       <c r="F102" s="3">
+        <v>1193100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-177300</v>
+      </c>
+      <c r="I102" s="3">
         <v>-64800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>151300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-9800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>105500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>9900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-159500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-108000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>68300</v>
       </c>
     </row>
